--- a/UD1/P1/COLORES.xlsx
+++ b/UD1/P1/COLORES.xlsx
@@ -24,255 +24,572 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="72">
   <si>
     <t>Categoría</t>
   </si>
   <si>
-    <t>Nombre del Color</t>
-  </si>
-  <si>
-    <t>Código / Valor</t>
-  </si>
-  <si>
-    <t>Función y Justificación Teórica de Clase</t>
-  </si>
-  <si>
-    <t>Primario 1</t>
-  </si>
-  <si>
     <t>Deep Space Black</t>
   </si>
   <si>
-    <t>RGB(8, 10, 16)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Fondo oscuro. Representa </t>
+    <t>Titanium White</t>
+  </si>
+  <si>
+    <t>Ion Blue</t>
+  </si>
+  <si>
+    <t>Cosmic Violet</t>
+  </si>
+  <si>
+    <t>Electric Cyan</t>
+  </si>
+  <si>
+    <t>Nebula Purple</t>
+  </si>
+  <si>
+    <t>Nombre de Marca (NÉBULA)</t>
+  </si>
+  <si>
+    <t>Código RGB</t>
+  </si>
+  <si>
+    <t>Código HEX</t>
+  </si>
+  <si>
+    <t>Nombre Real del Color (Estándar/Web)</t>
+  </si>
+  <si>
+    <t>Justificación Teórica y Función UI</t>
+  </si>
+  <si>
+    <t>Primario</t>
+  </si>
+  <si>
+    <t>RGB (8, 10, 16)</t>
+  </si>
+  <si>
+    <t>#080A10</t>
+  </si>
+  <si>
+    <t>RGB (243, 244, 246)</t>
+  </si>
+  <si>
+    <t>#F3F4F6</t>
+  </si>
+  <si>
+    <t>RGB (0, 150, 255)</t>
+  </si>
+  <si>
+    <t>#0096FF</t>
+  </si>
+  <si>
+    <t>RGB (123, 44, 191)</t>
+  </si>
+  <si>
+    <t>#7B2CBF</t>
+  </si>
+  <si>
+    <t>Secundario</t>
+  </si>
+  <si>
+    <t>Stellar Platinum</t>
+  </si>
+  <si>
+    <t>RGB (203, 207, 215)</t>
+  </si>
+  <si>
+    <t>#CBCFD7</t>
+  </si>
+  <si>
+    <t>Neutro metálico claro (+Value) para bordes de tarjetas, líneas técnicas y divisores.</t>
+  </si>
+  <si>
+    <t>Orbital Slate Blue</t>
+  </si>
+  <si>
+    <t>RGB (71, 88, 143)</t>
+  </si>
+  <si>
+    <t>#47588F</t>
+  </si>
+  <si>
+    <t>Azul desaturado (-Sat) para contenedores secundarios, módulos de telemetría y fondos medios.</t>
+  </si>
+  <si>
+    <t>RGB (0, 242, 254)</t>
+  </si>
+  <si>
+    <t>#00F2FE</t>
+  </si>
+  <si>
+    <t>Secundario derivado (+100% Sat / +Value). Reservado para botones de llamada a la acción (CTA) y acentos interactivos.</t>
+  </si>
+  <si>
+    <t>RGB (178, 75, 243)</t>
+  </si>
+  <si>
+    <t>#B24BF3</t>
+  </si>
+  <si>
+    <t>Complementario 1</t>
+  </si>
+  <si>
+    <t>Solar Amber</t>
+  </si>
+  <si>
+    <t>RGB (255, 165, 0)</t>
+  </si>
+  <si>
+    <t>#FFA500</t>
+  </si>
+  <si>
+    <t>Complementario 2</t>
+  </si>
+  <si>
+    <t>Solar Flare Gold</t>
+  </si>
+  <si>
+    <t>RGB (255, 204, 0)</t>
+  </si>
+  <si>
+    <t>#FFCC00</t>
+  </si>
+  <si>
+    <t>Complementario 3</t>
+  </si>
+  <si>
+    <t>Thruster Crimson</t>
+  </si>
+  <si>
+    <t>RGB (255, 68, 51)</t>
+  </si>
+  <si>
+    <t>#FF4433</t>
+  </si>
+  <si>
+    <t>Complementario 4</t>
+  </si>
+  <si>
+    <t>Supernova Coral</t>
+  </si>
+  <si>
+    <t>RGB (255, 112, 67)</t>
+  </si>
+  <si>
+    <t>#FF7043</t>
+  </si>
+  <si>
+    <r>
+      <t>Very Dark Blue / Jet Black</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Calibri Light"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> (Negro azabache con matiz azul)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Fondo base estructural. Representa </t>
     </r>
     <r>
       <rPr>
         <b/>
         <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Calibri Light"/>
+        <family val="2"/>
+        <scheme val="major"/>
       </rPr>
       <t>Elegancia, Poder y Estabilidad</t>
     </r>
     <r>
       <rPr>
         <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> (Valor ~0%). </t>
-    </r>
-  </si>
-  <si>
-    <t>Primario 2</t>
-  </si>
-  <si>
-    <t>Titanium White</t>
-  </si>
-  <si>
-    <t>RGB(243, 244, 246)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Textos y UI. Representa </t>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Calibri Light"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> (Valor ~0%).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Solitude / Anti-Flash White</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Calibri Light"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> (Blanco titanio frío)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Textos principales e iconos. Aporta </t>
     </r>
     <r>
       <rPr>
         <b/>
         <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Seguridad y Sencillez</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> (Valor ~100%, contraste máximo). </t>
-    </r>
-  </si>
-  <si>
-    <t>Primario 3</t>
-  </si>
-  <si>
-    <t>Ion Blue</t>
-  </si>
-  <si>
-    <t>RGB(0, 150, 255)</t>
-  </si>
-  <si>
-    <r>
-      <t>Identidad vehicular. Primario puro (</t>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Calibri Light"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Seguridad, Sencillez y Contraste puro</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Calibri Light"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Dodger Blue / Vivid Cerulean</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Calibri Light"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> (Azul cerúleo vivo)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Identidad vehicular y navegación. Representa </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Calibri Light"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Confianza y Seguridad vehicular</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Calibri Light"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Royal Violet / Blue-Violet</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Calibri Light"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> (Violeta real profundo)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Distinción de marca. Evoca </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Calibri Light"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Lujo, Realeza, Misterio y Sabiduría</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Calibri Light"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> tecnológica.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Lavender Gray / Light Slate Gray</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Calibri Light"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> (Gris pizarra claro con tinte lavanda)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Dark Slate Blue / Dusky Blue</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Calibri Light"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> (Azul pizarra oscuro apagado)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Vivid Cyan / Bright Turquoise</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Calibri Light"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> (Cian vívido / Turquesa brillante)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Medium Orchid / Bright Violet</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Calibri Light"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> (Orquídea brillante / Violeta medio)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Secundario derivado (+Value). Utilizado para degradados lumínicos, auras orbitales y estados </t>
     </r>
     <r>
       <rPr>
         <i/>
         <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Blue</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">). Aporta </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Confianza y Seguridad</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-  </si>
-  <si>
-    <t>Primario 4</t>
-  </si>
-  <si>
-    <t>Cosmic Violet</t>
-  </si>
-  <si>
-    <t>RGB(123, 44, 191)</t>
-  </si>
-  <si>
-    <r>
-      <t>Matiz distintivo (</t>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Calibri Light"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>hover</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Calibri Light"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Orange / Amber</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Calibri Light"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> (Naranja puro / Ámbar)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Opuesto al </t>
     </r>
     <r>
       <rPr>
         <i/>
         <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Violet</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">). Comunica </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Lujo, Vanguardia y Sabiduría</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">. </t>
-    </r>
-  </si>
-  <si>
-    <t>Secundario 1</t>
-  </si>
-  <si>
-    <t>Electric Cyan</t>
-  </si>
-  <si>
-    <t>RGB(0, 242, 254)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Acentos y botones CTA. Mezcla </t>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Calibri Light"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Ion Blue</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Calibri Light"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> en el círculo cromático. Reservado para avisos de precaución y telemetría de ruta.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Tangerine Yellow / Vivid Gold</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Calibri Light"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> (Amarillo oro vivo)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Opuesto al </t>
     </r>
     <r>
       <rPr>
         <i/>
         <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Green-Blue</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> de alta saturación (+100% sat). </t>
-    </r>
-  </si>
-  <si>
-    <t>Secundario 2</t>
-  </si>
-  <si>
-    <t>Nebula Purple</t>
-  </si>
-  <si>
-    <t>RGB(178, 75, 243)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Variación con mayor valor (+Value) del violeta para degradados y detalles UI. </t>
-  </si>
-  <si>
-    <t>Complementarios</t>
-  </si>
-  <si>
-    <t>Warm Orange / Amber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Opuesto en el círculo </t>
-  </si>
-  <si>
-    <r>
-      <t>Opuesto cromático al azul/cian</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">: reservado para advertencias, notificaciones de alerta y telemetría de vuelo en la interfaz. </t>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Calibri Light"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Cosmic Violet</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Calibri Light"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>. Reservado para estados de batería, recarga y alertas de potencia de vuelo.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Vermilion / Red-Orange</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Calibri Light"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> (Bermellón / Rojo-Naranja brillante)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Opuesto al </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Calibri Light"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Electric Cyan</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Calibri Light"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>. Reservado para el botón de parada de emergencia, abortar maniobra y advertencias críticas.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Coral / Bright Coral</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Calibri Light"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t xml:space="preserve"> (Coral rojizo)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Opuesto a los tonos azul-pizarra (</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Calibri Light"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Orbital Slate Blue</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Calibri Light"/>
+        <family val="2"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>). Reservado para insignias de notificaciones activas y avisos de llegada.</t>
     </r>
   </si>
 </sst>
@@ -280,7 +597,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -289,41 +606,65 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
       <b/>
       <sz val="12"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+      <scheme val="major"/>
     </font>
     <font>
       <sz val="12"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Courier New"/>
-      <family val="3"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+      <scheme val="major"/>
     </font>
     <font>
       <i/>
       <sz val="12"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
+      <scheme val="major"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF080A10"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -346,20 +687,129 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFC4C7C5"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFC4C7C5"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFC4C7C5"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFC4C7C5"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFC4C7C5"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="0"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color theme="0"/>
+      </top>
+      <bottom style="medium">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color theme="0"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="0"/>
+      </left>
+      <right style="medium">
+        <color theme="0"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="0"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -367,6 +817,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF080A10"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -641,122 +1096,279 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D8"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G13"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="4" width="31.28515625" customWidth="1"/>
+    <col min="1" max="1" width="11.42578125" style="5"/>
+    <col min="2" max="2" width="17.7109375" style="5" customWidth="1"/>
+    <col min="3" max="3" width="20.28515625" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.140625" style="5" customWidth="1"/>
+    <col min="5" max="5" width="13.140625" style="5" customWidth="1"/>
+    <col min="6" max="6" width="29.5703125" style="5" customWidth="1"/>
+    <col min="7" max="7" width="27.28515625" style="5" customWidth="1"/>
+    <col min="8" max="16384" width="11.42578125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="79.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:7" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="9"/>
+      <c r="B1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="63.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="6"/>
+      <c r="B2" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D2" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="63.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="63.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>3</v>
       </c>
+      <c r="D4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>56</v>
+      </c>
     </row>
-    <row r="2" spans="1:4" ht="158.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+    <row r="5" spans="1:7" ht="48" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>7</v>
+      <c r="D5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>58</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="174" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="158.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="142.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="158.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>20</v>
-      </c>
+    <row r="6" spans="1:7" ht="63.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B6" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="3" t="s">
         <v>23</v>
       </c>
+      <c r="E6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>25</v>
+      </c>
     </row>
-    <row r="7" spans="1:4" ht="158.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>24</v>
-      </c>
+    <row r="7" spans="1:7" ht="63.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="3" t="s">
         <v>27</v>
       </c>
+      <c r="E7" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>29</v>
+      </c>
     </row>
-    <row r="8" spans="1:4" ht="237" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
-        <v>28</v>
-      </c>
+    <row r="8" spans="1:7" ht="79.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="2" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="E8" s="3" t="s">
         <v>31</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="79.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="79.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" ht="63.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="79.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="79.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>71</v>
       </c>
     </row>
   </sheetData>
